--- a/administrative_forms/030_trailer_breakdown_process_checklist--administrative_forms.xlsx
+++ b/administrative_forms/030_trailer_breakdown_process_checklist--administrative_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -872,8 +872,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -935,12 +935,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'user_1'}</t>
+          <t>user_1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'User 1'}</t>
+          <t>User 1</t>
         </is>
       </c>
     </row>
@@ -952,12 +952,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'user_2'}</t>
+          <t>user_2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'User 2'}</t>
+          <t>User 2</t>
         </is>
       </c>
     </row>
@@ -969,12 +969,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'user_3'}</t>
+          <t>user_3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'User 3'}</t>
+          <t>User 3</t>
         </is>
       </c>
     </row>
@@ -986,12 +986,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'not_started'}</t>
+          <t>not_started</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Not Started'}</t>
+          <t>Not Started</t>
         </is>
       </c>
     </row>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'in_progress'}</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'In Progress'}</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
@@ -1020,12 +1020,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'complete'}</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Complete'}</t>
+          <t>Complete</t>
         </is>
       </c>
     </row>
